--- a/artfynd/A 26662-2025 artfynd.xlsx
+++ b/artfynd/A 26662-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126340520</v>
       </c>
       <c r="B2" t="n">
-        <v>106825</v>
+        <v>106828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26662-2025 artfynd.xlsx
+++ b/artfynd/A 26662-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126340520</v>
       </c>
       <c r="B2" t="n">
-        <v>106828</v>
+        <v>106837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26662-2025 artfynd.xlsx
+++ b/artfynd/A 26662-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126340520</v>
+        <v>148632</v>
       </c>
       <c r="B2" t="n">
-        <v>106837</v>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,26 +705,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strand, Vrm</t>
+          <t>Strand, 650 m VNV om, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>378752</v>
+        <v>378770</v>
       </c>
       <c r="R2" t="n">
-        <v>6591609</v>
+        <v>6591611</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,24 +752,24 @@
           <t>Värmskog</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>S-Gru-0033</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2007-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2007-07-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>näst intill beståndsbildande. Uppgiven koordinat 6595356 - 1333032.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,19 +780,542 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>skogsbryn och vägkanter</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Värmland Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Crister Albinsson, Stina Eriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126340504</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Strand, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>378752</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6591609</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Värmskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I bankslänt på norra sidan vägen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Anna Ljunggren</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Anna Ljunggren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126340505</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Strand, Strand, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>378740</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6591616</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Värmskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126340508</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Strand, Strand, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>378720</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6591628</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Värmskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126341321</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Strand, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>378754</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6591586</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Värmskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Står på den södra sidan av vägen i innerslänt.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Malin Schött, Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
